--- a/cet4/result/66_航海女神_碧海传奇的逆袭路/66_航海女神_碧海传奇的逆袭路_学习版.xlsx
+++ b/cet4/result/66_航海女神_碧海传奇的逆袭路/66_航海女神_碧海传奇的逆袭路_学习版.xlsx
@@ -397,647 +397,563 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D39"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>gate</v>
       </c>
       <c r="B2" t="str">
-        <v>gate</v>
+        <v>/ɡeɪt/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D2" t="str">
         <v>大门</v>
       </c>
-      <c r="D2" t="str">
-        <v>gate(大门)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>Tuesday</v>
       </c>
       <c r="B3" t="str">
-        <v>Tuesday</v>
+        <v>/'tjʊzdei/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>星期二</v>
       </c>
-      <c r="D3" t="str">
-        <v>Tuesday(星期二)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>winter</v>
       </c>
       <c r="B4" t="str">
-        <v>winter</v>
+        <v>/ˈwɪntər/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vi./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>冬天</v>
       </c>
-      <c r="D4" t="str">
-        <v>winter(冬天)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>very</v>
       </c>
       <c r="B5" t="str">
-        <v>very</v>
+        <v>/ˈveri/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D5" t="str">
         <v>非常</v>
       </c>
-      <c r="D5" t="str">
-        <v>very(非常)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>sailor</v>
       </c>
       <c r="B6" t="str">
-        <v>sailor</v>
+        <v>/ˈseɪlər/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>水手</v>
       </c>
-      <c r="D6" t="str">
-        <v>sailor(水手)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>equal</v>
       </c>
       <c r="B7" t="str">
-        <v>equal</v>
+        <v>/ˈiːkwəl/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>平等</v>
       </c>
-      <c r="D7" t="str">
-        <v>equal(平等)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>forest</v>
       </c>
       <c r="B8" t="str">
-        <v>forest</v>
+        <v>/ˈfɔːrɪst/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D8" t="str">
         <v>森林</v>
       </c>
-      <c r="D8" t="str">
-        <v>forest(森林)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>climate</v>
       </c>
       <c r="B9" t="str">
-        <v>climate</v>
+        <v>/ˈklaɪmət/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>气候</v>
       </c>
-      <c r="D9" t="str">
-        <v>climate(气候)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>acute</v>
       </c>
       <c r="B10" t="str">
-        <v>acute</v>
+        <v>/əˈkjuːt/</v>
       </c>
       <c r="C10" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>严重</v>
       </c>
-      <c r="D10" t="str">
-        <v>acute(严重)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>more</v>
       </c>
       <c r="B11" t="str">
-        <v>more</v>
+        <v>/mɔːr/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./v./adj./adv./pron.</v>
+      </c>
+      <c r="D11" t="str">
         <v>更多</v>
       </c>
-      <c r="D11" t="str">
-        <v>more(更多)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>mill</v>
       </c>
       <c r="B12" t="str">
-        <v>mill</v>
+        <v>/mɪl/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D12" t="str">
         <v>工厂</v>
       </c>
-      <c r="D12" t="str">
-        <v>mill(工厂)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>industry</v>
       </c>
       <c r="B13" t="str">
-        <v>industry</v>
+        <v>/ˈɪndəstri/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>工业</v>
       </c>
-      <c r="D13" t="str">
-        <v>industry(工业)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>joy</v>
       </c>
       <c r="B14" t="str">
-        <v>joy</v>
+        <v>/dʒɔɪ/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D14" t="str">
         <v>欢乐</v>
       </c>
-      <c r="D14" t="str">
-        <v>joy(欢乐)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>lunch</v>
       </c>
       <c r="B15" t="str">
-        <v>lunch</v>
+        <v>/lʌntʃ/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D15" t="str">
         <v>午餐</v>
       </c>
-      <c r="D15" t="str">
-        <v>lunch(午餐)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>notice</v>
       </c>
       <c r="B16" t="str">
-        <v>notice</v>
+        <v>/ˈnəʊtɪs/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D16" t="str">
         <v>注意</v>
       </c>
-      <c r="D16" t="str">
-        <v>notice(注意)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>approach</v>
       </c>
       <c r="B17" t="str">
-        <v>approach</v>
+        <v>/əˈproʊtʃ/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D17" t="str">
         <v>接近</v>
       </c>
-      <c r="D17" t="str">
-        <v>approach(接近)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>throat</v>
       </c>
       <c r="B18" t="str">
-        <v>throat</v>
+        <v>/θroʊt/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D18" t="str">
         <v>喉咙</v>
       </c>
-      <c r="D18" t="str">
-        <v>throat(喉咙)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>drink</v>
       </c>
       <c r="B19" t="str">
-        <v>drink</v>
+        <v>/drɪŋk/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D19" t="str">
         <v>喝</v>
       </c>
-      <c r="D19" t="str">
-        <v>drink(喝)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>shepherd</v>
       </c>
       <c r="B20" t="str">
-        <v>shepherd</v>
+        <v>/ˈʃepərd/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D20" t="str">
         <v>牧羊人</v>
       </c>
-      <c r="D20" t="str">
-        <v>shepherd(牧羊人)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>anxious</v>
       </c>
       <c r="B21" t="str">
-        <v>anxious</v>
+        <v>/ˈæŋkʃəs/</v>
       </c>
       <c r="C21" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>焦虑的</v>
       </c>
-      <c r="D21" t="str">
-        <v>anxious(焦虑的)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>simple</v>
       </c>
       <c r="B22" t="str">
-        <v>simple</v>
+        <v>/ˈsɪmpl/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>简单</v>
       </c>
-      <c r="D22" t="str">
-        <v>simple(简单)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>minister</v>
       </c>
       <c r="B23" t="str">
-        <v>minister</v>
+        <v>/ˈmɪnɪstər/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D23" t="str">
         <v>部长</v>
       </c>
-      <c r="D23" t="str">
-        <v>minister(部长)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>expression</v>
       </c>
       <c r="B24" t="str">
-        <v>very</v>
+        <v>/ɪkˈspreʃn/</v>
       </c>
       <c r="C24" t="str">
-        <v>非常</v>
+        <v>n.</v>
       </c>
       <c r="D24" t="str">
-        <v>very(非常)📢</v>
+        <v>表达</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>activity</v>
       </c>
       <c r="B25" t="str">
-        <v>expression</v>
+        <v>/ækˈtɪvəti/</v>
       </c>
       <c r="C25" t="str">
-        <v>表达</v>
+        <v>n.</v>
       </c>
       <c r="D25" t="str">
-        <v>expression(表达)📢</v>
+        <v>活动</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>carry</v>
       </c>
       <c r="B26" t="str">
-        <v>activity</v>
+        <v>/ˈkæri/</v>
       </c>
       <c r="C26" t="str">
-        <v>活动</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D26" t="str">
-        <v>activity(活动)📢</v>
+        <v>携带</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>white</v>
       </c>
       <c r="B27" t="str">
-        <v>carry</v>
+        <v>/waɪt/</v>
       </c>
       <c r="C27" t="str">
-        <v>携带</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D27" t="str">
-        <v>carry(携带)📢</v>
+        <v>白色</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>garden</v>
       </c>
       <c r="B28" t="str">
-        <v>white</v>
+        <v>/ˈɡɑːrdn/</v>
       </c>
       <c r="C28" t="str">
-        <v>白色</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D28" t="str">
-        <v>white(白色)📢</v>
+        <v>花园</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>technology</v>
       </c>
       <c r="B29" t="str">
-        <v>garden</v>
+        <v>/tekˈnɑːlədʒi/</v>
       </c>
       <c r="C29" t="str">
-        <v>花园</v>
+        <v>n.</v>
       </c>
       <c r="D29" t="str">
-        <v>garden(花园)📢</v>
+        <v>技术</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>deadly</v>
       </c>
       <c r="B30" t="str">
-        <v>technology</v>
+        <v>/ˈdedli/</v>
       </c>
       <c r="C30" t="str">
-        <v>技术</v>
+        <v>v./adj./adv.</v>
       </c>
       <c r="D30" t="str">
-        <v>technology(技术)📢</v>
+        <v>致命</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>angel</v>
       </c>
       <c r="B31" t="str">
-        <v>deadly</v>
+        <v>/ˈeɪndʒl/</v>
       </c>
       <c r="C31" t="str">
-        <v>致命</v>
+        <v>n.</v>
       </c>
       <c r="D31" t="str">
-        <v>deadly(致命)📢</v>
+        <v>天使</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>hamburger</v>
       </c>
       <c r="B32" t="str">
-        <v>forest</v>
+        <v>/ˈhæmbɜːrɡər/</v>
       </c>
       <c r="C32" t="str">
-        <v>森林</v>
+        <v>n.</v>
       </c>
       <c r="D32" t="str">
-        <v>forest(森林)📢</v>
+        <v>汉堡包</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>rug</v>
       </c>
       <c r="B33" t="str">
-        <v>garden</v>
+        <v>/rʌɡ/</v>
       </c>
       <c r="C33" t="str">
-        <v>花园</v>
+        <v>n.</v>
       </c>
       <c r="D33" t="str">
-        <v>garden(花园)📢</v>
+        <v>地毯</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>city</v>
       </c>
       <c r="B34" t="str">
-        <v>angel</v>
+        <v>/ˈsɪti/</v>
       </c>
       <c r="C34" t="str">
-        <v>天使</v>
+        <v>n./adj.</v>
       </c>
       <c r="D34" t="str">
-        <v>angel(天使)📢</v>
+        <v>城市</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>lay</v>
       </c>
       <c r="B35" t="str">
-        <v>hamburger</v>
+        <v>/leɪ/</v>
       </c>
       <c r="C35" t="str">
-        <v>汉堡包</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D35" t="str">
-        <v>hamburger(汉堡包)📢</v>
+        <v>放置</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>weakness</v>
       </c>
       <c r="B36" t="str">
-        <v>rug</v>
+        <v>/ˈwiːknəs/</v>
       </c>
       <c r="C36" t="str">
-        <v>地毯</v>
+        <v>n.</v>
       </c>
       <c r="D36" t="str">
-        <v>rug(地毯)📢</v>
+        <v>弱点</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>psychological</v>
       </c>
       <c r="B37" t="str">
-        <v>city</v>
+        <v>/ˌsaɪkəˈlɑːdʒɪkl/</v>
       </c>
       <c r="C37" t="str">
-        <v>城市</v>
+        <v>adj.</v>
       </c>
       <c r="D37" t="str">
-        <v>city(城市)📢</v>
+        <v>心理</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>restraint</v>
       </c>
       <c r="B38" t="str">
-        <v>angel</v>
+        <v>/rɪˈstreɪnt/</v>
       </c>
       <c r="C38" t="str">
-        <v>天使</v>
+        <v>n.</v>
       </c>
       <c r="D38" t="str">
-        <v>angel(天使)📢</v>
+        <v>克制</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>quotation</v>
       </c>
       <c r="B39" t="str">
-        <v>lay</v>
+        <v>/kwoʊˈteɪʃn/</v>
       </c>
       <c r="C39" t="str">
-        <v>放置</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>lay(放置)📢</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>weakness</v>
-      </c>
-      <c r="C40" t="str">
-        <v>弱点</v>
-      </c>
-      <c r="D40" t="str">
-        <v>weakness(弱点)📢</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>psychological</v>
-      </c>
-      <c r="C41" t="str">
-        <v>心理</v>
-      </c>
-      <c r="D41" t="str">
-        <v>psychological(心理)📢</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>restraint</v>
-      </c>
-      <c r="C42" t="str">
-        <v>克制</v>
-      </c>
-      <c r="D42" t="str">
-        <v>restraint(克制)📢</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>winter</v>
-      </c>
-      <c r="C43" t="str">
-        <v>冬天</v>
-      </c>
-      <c r="D43" t="str">
-        <v>winter(冬天)📢</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>quotation</v>
-      </c>
-      <c r="C44" t="str">
         <v>引用语</v>
-      </c>
-      <c r="D44" t="str">
-        <v>quotation(引用语)📢</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>gate</v>
-      </c>
-      <c r="C45" t="str">
-        <v>大门</v>
-      </c>
-      <c r="D45" t="str">
-        <v>gate(大门)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D39"/>
   </ignoredErrors>
 </worksheet>
 </file>